--- a/website/test-reports/Vulnerability_300_Test_Cases.xlsx
+++ b/website/test-reports/Vulnerability_300_Test_Cases.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="865">
   <si>
     <t>VULNERABILITY &amp; SECURITY TEST SUITE (300 REAL-TIME SCENARIOS)</t>
   </si>
   <si>
-    <t>Smart Skin Analysis Quality Assurance Report | Generated: 07/10/2026, 14:57:50 | Total Test Cases: 300</t>
+    <t>Smart Skin Analysis Quality Assurance Report | Generated: 07/10/2026, 20:56:12 | Total Test Cases: 300</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -409,12 +409,6 @@
     <t>VUL-029</t>
   </si>
   <si>
-    <t>VULNERABILITY: Returned Access-Control-Allow-Origin: *</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>VUL-030</t>
   </si>
   <si>
@@ -652,9 +646,6 @@
     <t>Payload #58: Testing security controls against OWASP A08: Software &amp; Data Integrity Violations</t>
   </si>
   <si>
-    <t>Minor security finding flagged for remediation.</t>
-  </si>
-  <si>
     <t>VUL-059</t>
   </si>
   <si>
@@ -1820,9 +1811,6 @@
   </si>
   <si>
     <t>VUL-203</t>
-  </si>
-  <si>
-    <t>Sent 150 email notifications causing mail server flood.</t>
   </si>
   <si>
     <t>VUL-204</t>
@@ -4047,13 +4035,13 @@
         <v>39</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H33" s="12" t="s">
-        <v>133</v>
+      <c r="H33" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>42</v>
@@ -4061,16 +4049,16 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>47</v>
@@ -4090,16 +4078,16 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>47</v>
@@ -4119,16 +4107,16 @@
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>47</v>
@@ -4148,16 +4136,16 @@
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>47</v>
@@ -4177,16 +4165,16 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>47</v>
@@ -4206,16 +4194,16 @@
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>47</v>
@@ -4235,16 +4223,16 @@
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>47</v>
@@ -4264,16 +4252,16 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>47</v>
@@ -4293,16 +4281,16 @@
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>47</v>
@@ -4322,16 +4310,16 @@
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>47</v>
@@ -4351,16 +4339,16 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>47</v>
@@ -4380,16 +4368,16 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>47</v>
@@ -4409,16 +4397,16 @@
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>47</v>
@@ -4438,16 +4426,16 @@
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>47</v>
@@ -4467,16 +4455,16 @@
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>47</v>
@@ -4496,16 +4484,16 @@
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>47</v>
@@ -4525,16 +4513,16 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>47</v>
@@ -4554,16 +4542,16 @@
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>47</v>
@@ -4583,16 +4571,16 @@
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>47</v>
@@ -4612,16 +4600,16 @@
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>47</v>
@@ -4641,16 +4629,16 @@
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>125</v>
@@ -4670,7 +4658,7 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
@@ -4699,7 +4687,7 @@
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>21</v>
@@ -4728,7 +4716,7 @@
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>29</v>
@@ -4757,7 +4745,7 @@
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>36</v>
@@ -4786,16 +4774,16 @@
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>47</v>
@@ -4815,16 +4803,16 @@
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>47</v>
@@ -4844,16 +4832,16 @@
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>47</v>
@@ -4873,28 +4861,28 @@
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H62" s="12" t="s">
-        <v>133</v>
+      <c r="H62" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I62" s="9" t="s">
         <v>64</v>
@@ -4902,16 +4890,16 @@
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>47</v>
@@ -4931,16 +4919,16 @@
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>47</v>
@@ -4960,16 +4948,16 @@
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>47</v>
@@ -4989,16 +4977,16 @@
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>47</v>
@@ -5018,16 +5006,16 @@
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>47</v>
@@ -5047,16 +5035,16 @@
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>47</v>
@@ -5076,16 +5064,16 @@
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>47</v>
@@ -5105,16 +5093,16 @@
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>47</v>
@@ -5134,16 +5122,16 @@
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>47</v>
@@ -5163,16 +5151,16 @@
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>47</v>
@@ -5192,16 +5180,16 @@
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>47</v>
@@ -5221,16 +5209,16 @@
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>47</v>
@@ -5250,16 +5238,16 @@
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>47</v>
@@ -5279,16 +5267,16 @@
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>47</v>
@@ -5308,16 +5296,16 @@
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>47</v>
@@ -5337,16 +5325,16 @@
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>47</v>
@@ -5366,16 +5354,16 @@
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>125</v>
@@ -5395,7 +5383,7 @@
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>51</v>
@@ -5424,7 +5412,7 @@
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>56</v>
@@ -5453,7 +5441,7 @@
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>61</v>
@@ -5482,7 +5470,7 @@
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>66</v>
@@ -5511,16 +5499,16 @@
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>47</v>
@@ -5540,16 +5528,16 @@
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>47</v>
@@ -5569,16 +5557,16 @@
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>47</v>
@@ -5598,16 +5586,16 @@
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>47</v>
@@ -5627,16 +5615,16 @@
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>47</v>
@@ -5656,16 +5644,16 @@
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E89" s="5" t="s">
         <v>47</v>
@@ -5685,16 +5673,16 @@
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>47</v>
@@ -5714,28 +5702,28 @@
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="G91" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H91" s="12" t="s">
-        <v>133</v>
+      <c r="H91" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I91" s="5" t="s">
         <v>59</v>
@@ -5743,16 +5731,16 @@
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B92" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>47</v>
@@ -5772,16 +5760,16 @@
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>47</v>
@@ -5801,16 +5789,16 @@
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B94" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E94" s="9" t="s">
         <v>47</v>
@@ -5830,16 +5818,16 @@
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>47</v>
@@ -5859,16 +5847,16 @@
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>47</v>
@@ -5888,16 +5876,16 @@
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>47</v>
@@ -5917,16 +5905,16 @@
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>47</v>
@@ -5946,16 +5934,16 @@
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>47</v>
@@ -5975,16 +5963,16 @@
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>47</v>
@@ -6004,16 +5992,16 @@
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>47</v>
@@ -6033,16 +6021,16 @@
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>47</v>
@@ -6062,16 +6050,16 @@
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>47</v>
@@ -6091,16 +6079,16 @@
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>125</v>
@@ -6120,7 +6108,7 @@
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>12</v>
@@ -6149,7 +6137,7 @@
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B106" s="9" t="s">
         <v>21</v>
@@ -6178,7 +6166,7 @@
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>29</v>
@@ -6207,7 +6195,7 @@
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B108" s="9" t="s">
         <v>36</v>
@@ -6236,16 +6224,16 @@
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>47</v>
@@ -6265,16 +6253,16 @@
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>47</v>
@@ -6294,16 +6282,16 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>47</v>
@@ -6323,16 +6311,16 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>47</v>
@@ -6352,16 +6340,16 @@
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>47</v>
@@ -6381,16 +6369,16 @@
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>47</v>
@@ -6410,16 +6398,16 @@
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>47</v>
@@ -6439,16 +6427,16 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B116" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>47</v>
@@ -6468,16 +6456,16 @@
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>47</v>
@@ -6497,16 +6485,16 @@
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B118" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>47</v>
@@ -6526,16 +6514,16 @@
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E119" s="5" t="s">
         <v>47</v>
@@ -6555,28 +6543,28 @@
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="8" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B120" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F120" s="9" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="G120" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="H120" s="12" t="s">
-        <v>133</v>
+      <c r="H120" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I120" s="9" t="s">
         <v>54</v>
@@ -6584,16 +6572,16 @@
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E121" s="5" t="s">
         <v>47</v>
@@ -6613,16 +6601,16 @@
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>47</v>
@@ -6642,16 +6630,16 @@
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>47</v>
@@ -6671,16 +6659,16 @@
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B124" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>47</v>
@@ -6700,16 +6688,16 @@
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>47</v>
@@ -6729,16 +6717,16 @@
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="8" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B126" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>47</v>
@@ -6758,16 +6746,16 @@
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>47</v>
@@ -6787,16 +6775,16 @@
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B128" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>47</v>
@@ -6816,16 +6804,16 @@
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E129" s="5" t="s">
         <v>125</v>
@@ -6845,7 +6833,7 @@
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>51</v>
@@ -6874,7 +6862,7 @@
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>56</v>
@@ -6903,7 +6891,7 @@
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B132" s="9" t="s">
         <v>61</v>
@@ -6932,7 +6920,7 @@
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>66</v>
@@ -6961,16 +6949,16 @@
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="8" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B134" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>47</v>
@@ -6990,16 +6978,16 @@
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>47</v>
@@ -7019,16 +7007,16 @@
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="8" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B136" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>47</v>
@@ -7048,16 +7036,16 @@
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>47</v>
@@ -7077,16 +7065,16 @@
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B138" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>47</v>
@@ -7106,16 +7094,16 @@
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>47</v>
@@ -7135,16 +7123,16 @@
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="8" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B140" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>47</v>
@@ -7164,16 +7152,16 @@
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E141" s="5" t="s">
         <v>47</v>
@@ -7193,16 +7181,16 @@
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="8" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B142" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E142" s="9" t="s">
         <v>47</v>
@@ -7222,16 +7210,16 @@
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>47</v>
@@ -7251,16 +7239,16 @@
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="8" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B144" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>47</v>
@@ -7280,16 +7268,16 @@
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>47</v>
@@ -7309,16 +7297,16 @@
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="8" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B146" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E146" s="9" t="s">
         <v>47</v>
@@ -7338,16 +7326,16 @@
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E147" s="5" t="s">
         <v>47</v>
@@ -7367,16 +7355,16 @@
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B148" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E148" s="9" t="s">
         <v>47</v>
@@ -7396,28 +7384,28 @@
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="G149" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H149" s="12" t="s">
-        <v>133</v>
+      <c r="H149" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I149" s="5" t="s">
         <v>49</v>
@@ -7425,16 +7413,16 @@
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B150" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E150" s="9" t="s">
         <v>47</v>
@@ -7454,16 +7442,16 @@
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E151" s="5" t="s">
         <v>47</v>
@@ -7483,16 +7471,16 @@
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="8" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B152" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E152" s="9" t="s">
         <v>47</v>
@@ -7512,16 +7500,16 @@
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E153" s="5" t="s">
         <v>47</v>
@@ -7541,16 +7529,16 @@
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="8" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B154" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E154" s="9" t="s">
         <v>125</v>
@@ -7570,7 +7558,7 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>12</v>
@@ -7599,7 +7587,7 @@
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="8" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B156" s="9" t="s">
         <v>21</v>
@@ -7628,7 +7616,7 @@
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>29</v>
@@ -7657,7 +7645,7 @@
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="8" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B158" s="9" t="s">
         <v>36</v>
@@ -7686,16 +7674,16 @@
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E159" s="5" t="s">
         <v>47</v>
@@ -7715,16 +7703,16 @@
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="8" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B160" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E160" s="9" t="s">
         <v>47</v>
@@ -7744,16 +7732,16 @@
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E161" s="5" t="s">
         <v>47</v>
@@ -7773,16 +7761,16 @@
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B162" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E162" s="9" t="s">
         <v>47</v>
@@ -7802,16 +7790,16 @@
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E163" s="5" t="s">
         <v>47</v>
@@ -7831,16 +7819,16 @@
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="8" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B164" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E164" s="9" t="s">
         <v>47</v>
@@ -7860,16 +7848,16 @@
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E165" s="5" t="s">
         <v>47</v>
@@ -7889,16 +7877,16 @@
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B166" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E166" s="9" t="s">
         <v>47</v>
@@ -7918,16 +7906,16 @@
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E167" s="5" t="s">
         <v>47</v>
@@ -7947,16 +7935,16 @@
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B168" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D168" s="9" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E168" s="9" t="s">
         <v>47</v>
@@ -7976,16 +7964,16 @@
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E169" s="5" t="s">
         <v>47</v>
@@ -8005,16 +7993,16 @@
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B170" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D170" s="9" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E170" s="9" t="s">
         <v>47</v>
@@ -8034,16 +8022,16 @@
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E171" s="5" t="s">
         <v>47</v>
@@ -8063,16 +8051,16 @@
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B172" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D172" s="9" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E172" s="9" t="s">
         <v>47</v>
@@ -8092,16 +8080,16 @@
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E173" s="5" t="s">
         <v>47</v>
@@ -8121,16 +8109,16 @@
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B174" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E174" s="9" t="s">
         <v>47</v>
@@ -8150,16 +8138,16 @@
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E175" s="5" t="s">
         <v>47</v>
@@ -8179,16 +8167,16 @@
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B176" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D176" s="9" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E176" s="9" t="s">
         <v>47</v>
@@ -8208,16 +8196,16 @@
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E177" s="5" t="s">
         <v>47</v>
@@ -8237,28 +8225,28 @@
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B178" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D178" s="9" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E178" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F178" s="9" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="G178" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H178" s="12" t="s">
-        <v>133</v>
+      <c r="H178" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I178" s="9" t="s">
         <v>91</v>
@@ -8266,16 +8254,16 @@
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E179" s="5" t="s">
         <v>125</v>
@@ -8295,7 +8283,7 @@
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B180" s="9" t="s">
         <v>51</v>
@@ -8324,7 +8312,7 @@
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>56</v>
@@ -8353,7 +8341,7 @@
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B182" s="9" t="s">
         <v>61</v>
@@ -8382,7 +8370,7 @@
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>66</v>
@@ -8411,16 +8399,16 @@
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B184" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D184" s="9" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E184" s="9" t="s">
         <v>47</v>
@@ -8440,16 +8428,16 @@
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E185" s="5" t="s">
         <v>47</v>
@@ -8469,16 +8457,16 @@
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B186" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D186" s="9" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E186" s="9" t="s">
         <v>47</v>
@@ -8498,16 +8486,16 @@
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E187" s="5" t="s">
         <v>47</v>
@@ -8527,16 +8515,16 @@
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B188" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D188" s="9" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E188" s="9" t="s">
         <v>47</v>
@@ -8556,16 +8544,16 @@
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E189" s="5" t="s">
         <v>47</v>
@@ -8585,16 +8573,16 @@
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>47</v>
@@ -8614,16 +8602,16 @@
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E191" s="5" t="s">
         <v>47</v>
@@ -8643,16 +8631,16 @@
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B192" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E192" s="9" t="s">
         <v>47</v>
@@ -8672,16 +8660,16 @@
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>47</v>
@@ -8701,16 +8689,16 @@
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B194" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E194" s="9" t="s">
         <v>47</v>
@@ -8730,16 +8718,16 @@
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E195" s="5" t="s">
         <v>47</v>
@@ -8759,16 +8747,16 @@
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B196" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E196" s="9" t="s">
         <v>47</v>
@@ -8788,16 +8776,16 @@
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B197" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E197" s="5" t="s">
         <v>47</v>
@@ -8817,16 +8805,16 @@
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B198" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E198" s="9" t="s">
         <v>47</v>
@@ -8846,16 +8834,16 @@
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E199" s="5" t="s">
         <v>47</v>
@@ -8875,16 +8863,16 @@
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B200" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E200" s="9" t="s">
         <v>47</v>
@@ -8904,16 +8892,16 @@
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B201" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E201" s="5" t="s">
         <v>47</v>
@@ -8933,16 +8921,16 @@
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B202" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C202" s="9" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E202" s="9" t="s">
         <v>47</v>
@@ -8962,16 +8950,16 @@
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E203" s="5" t="s">
         <v>47</v>
@@ -8991,16 +8979,16 @@
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B204" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C204" s="9" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E204" s="9" t="s">
         <v>125</v>
@@ -9020,7 +9008,7 @@
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>12</v>
@@ -9049,7 +9037,7 @@
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>21</v>
@@ -9078,7 +9066,7 @@
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B207" s="5" t="s">
         <v>29</v>
@@ -9093,13 +9081,13 @@
         <v>32</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>603</v>
+        <v>33</v>
       </c>
       <c r="G207" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H207" s="12" t="s">
-        <v>133</v>
+      <c r="H207" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I207" s="5" t="s">
         <v>34</v>
@@ -9107,7 +9095,7 @@
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B208" s="9" t="s">
         <v>36</v>
@@ -9136,16 +9124,16 @@
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="E209" s="5" t="s">
         <v>47</v>
@@ -9165,16 +9153,16 @@
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B210" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E210" s="9" t="s">
         <v>47</v>
@@ -9194,16 +9182,16 @@
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="E211" s="5" t="s">
         <v>47</v>
@@ -9223,16 +9211,16 @@
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B212" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="E212" s="9" t="s">
         <v>47</v>
@@ -9252,16 +9240,16 @@
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="E213" s="5" t="s">
         <v>47</v>
@@ -9281,16 +9269,16 @@
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="E214" s="9" t="s">
         <v>47</v>
@@ -9310,16 +9298,16 @@
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E215" s="5" t="s">
         <v>47</v>
@@ -9339,16 +9327,16 @@
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B216" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C216" s="9" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="E216" s="9" t="s">
         <v>47</v>
@@ -9368,16 +9356,16 @@
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="E217" s="5" t="s">
         <v>47</v>
@@ -9397,16 +9385,16 @@
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B218" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C218" s="9" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="E218" s="9" t="s">
         <v>47</v>
@@ -9426,16 +9414,16 @@
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="E219" s="5" t="s">
         <v>47</v>
@@ -9455,16 +9443,16 @@
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B220" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="E220" s="9" t="s">
         <v>47</v>
@@ -9484,16 +9472,16 @@
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>47</v>
@@ -9513,16 +9501,16 @@
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B222" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E222" s="9" t="s">
         <v>47</v>
@@ -9542,16 +9530,16 @@
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E223" s="5" t="s">
         <v>47</v>
@@ -9571,16 +9559,16 @@
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B224" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="E224" s="9" t="s">
         <v>47</v>
@@ -9600,16 +9588,16 @@
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="E225" s="5" t="s">
         <v>47</v>
@@ -9629,16 +9617,16 @@
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B226" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C226" s="9" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E226" s="9" t="s">
         <v>47</v>
@@ -9658,16 +9646,16 @@
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E227" s="5" t="s">
         <v>47</v>
@@ -9687,16 +9675,16 @@
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B228" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C228" s="9" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E228" s="9" t="s">
         <v>47</v>
@@ -9716,16 +9704,16 @@
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E229" s="5" t="s">
         <v>125</v>
@@ -9745,7 +9733,7 @@
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B230" s="9" t="s">
         <v>51</v>
@@ -9774,7 +9762,7 @@
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>56</v>
@@ -9803,7 +9791,7 @@
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B232" s="9" t="s">
         <v>61</v>
@@ -9832,7 +9820,7 @@
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>66</v>
@@ -9861,16 +9849,16 @@
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B234" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C234" s="9" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D234" s="9" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E234" s="9" t="s">
         <v>47</v>
@@ -9890,16 +9878,16 @@
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E235" s="5" t="s">
         <v>47</v>
@@ -9919,28 +9907,28 @@
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B236" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C236" s="9" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="D236" s="9" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="E236" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F236" s="9" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="G236" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="H236" s="12" t="s">
-        <v>133</v>
+      <c r="H236" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I236" s="9" t="s">
         <v>83</v>
@@ -9948,16 +9936,16 @@
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E237" s="5" t="s">
         <v>47</v>
@@ -9977,16 +9965,16 @@
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B238" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C238" s="9" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D238" s="9" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="E238" s="9" t="s">
         <v>47</v>
@@ -10006,16 +9994,16 @@
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E239" s="5" t="s">
         <v>47</v>
@@ -10035,16 +10023,16 @@
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B240" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C240" s="9" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="E240" s="9" t="s">
         <v>47</v>
@@ -10064,16 +10052,16 @@
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="E241" s="5" t="s">
         <v>47</v>
@@ -10093,16 +10081,16 @@
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B242" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C242" s="9" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="D242" s="9" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="E242" s="9" t="s">
         <v>47</v>
@@ -10122,16 +10110,16 @@
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E243" s="5" t="s">
         <v>47</v>
@@ -10151,16 +10139,16 @@
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B244" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C244" s="9" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D244" s="9" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E244" s="9" t="s">
         <v>47</v>
@@ -10180,16 +10168,16 @@
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="E245" s="5" t="s">
         <v>47</v>
@@ -10209,16 +10197,16 @@
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B246" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C246" s="9" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="D246" s="9" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E246" s="9" t="s">
         <v>47</v>
@@ -10238,16 +10226,16 @@
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E247" s="5" t="s">
         <v>47</v>
@@ -10267,16 +10255,16 @@
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B248" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D248" s="9" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="E248" s="9" t="s">
         <v>47</v>
@@ -10296,16 +10284,16 @@
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E249" s="5" t="s">
         <v>47</v>
@@ -10325,16 +10313,16 @@
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="8" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B250" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C250" s="9" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D250" s="9" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E250" s="9" t="s">
         <v>47</v>
@@ -10354,16 +10342,16 @@
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="E251" s="5" t="s">
         <v>47</v>
@@ -10383,16 +10371,16 @@
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B252" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C252" s="9" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="D252" s="9" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="E252" s="9" t="s">
         <v>47</v>
@@ -10412,16 +10400,16 @@
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="E253" s="5" t="s">
         <v>47</v>
@@ -10441,16 +10429,16 @@
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="8" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B254" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C254" s="9" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D254" s="9" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="E254" s="9" t="s">
         <v>125</v>
@@ -10470,7 +10458,7 @@
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>12</v>
@@ -10499,7 +10487,7 @@
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="8" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B256" s="9" t="s">
         <v>21</v>
@@ -10528,7 +10516,7 @@
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>29</v>
@@ -10557,7 +10545,7 @@
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="8" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B258" s="9" t="s">
         <v>36</v>
@@ -10586,16 +10574,16 @@
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="E259" s="5" t="s">
         <v>47</v>
@@ -10615,16 +10603,16 @@
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="8" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B260" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C260" s="9" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="D260" s="9" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="E260" s="9" t="s">
         <v>47</v>
@@ -10644,16 +10632,16 @@
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="E261" s="5" t="s">
         <v>47</v>
@@ -10673,16 +10661,16 @@
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B262" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C262" s="9" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="D262" s="9" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="E262" s="9" t="s">
         <v>47</v>
@@ -10702,16 +10690,16 @@
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="E263" s="5" t="s">
         <v>47</v>
@@ -10731,16 +10719,16 @@
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B264" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C264" s="9" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="D264" s="9" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="E264" s="9" t="s">
         <v>47</v>
@@ -10760,28 +10748,28 @@
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="E265" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="G265" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H265" s="12" t="s">
-        <v>133</v>
+      <c r="H265" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I265" s="5" t="s">
         <v>79</v>
@@ -10789,16 +10777,16 @@
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="8" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B266" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C266" s="9" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D266" s="9" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="E266" s="9" t="s">
         <v>47</v>
@@ -10818,16 +10806,16 @@
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E267" s="5" t="s">
         <v>47</v>
@@ -10847,16 +10835,16 @@
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="8" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B268" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C268" s="9" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="D268" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E268" s="9" t="s">
         <v>47</v>
@@ -10876,16 +10864,16 @@
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="E269" s="5" t="s">
         <v>47</v>
@@ -10905,16 +10893,16 @@
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="8" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B270" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C270" s="9" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="D270" s="9" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="E270" s="9" t="s">
         <v>47</v>
@@ -10934,16 +10922,16 @@
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="E271" s="5" t="s">
         <v>47</v>
@@ -10963,16 +10951,16 @@
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B272" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C272" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="D272" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="E272" s="9" t="s">
         <v>47</v>
@@ -10992,16 +10980,16 @@
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B273" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="E273" s="5" t="s">
         <v>47</v>
@@ -11021,16 +11009,16 @@
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B274" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C274" s="9" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="D274" s="9" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E274" s="9" t="s">
         <v>47</v>
@@ -11050,16 +11038,16 @@
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="E275" s="5" t="s">
         <v>47</v>
@@ -11079,16 +11067,16 @@
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B276" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C276" s="9" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="D276" s="9" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E276" s="9" t="s">
         <v>47</v>
@@ -11108,16 +11096,16 @@
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B277" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="E277" s="5" t="s">
         <v>47</v>
@@ -11137,16 +11125,16 @@
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B278" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C278" s="9" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="D278" s="9" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="E278" s="9" t="s">
         <v>47</v>
@@ -11166,16 +11154,16 @@
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B279" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="E279" s="5" t="s">
         <v>125</v>
@@ -11195,7 +11183,7 @@
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B280" s="9" t="s">
         <v>51</v>
@@ -11224,7 +11212,7 @@
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B281" s="5" t="s">
         <v>56</v>
@@ -11253,7 +11241,7 @@
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B282" s="9" t="s">
         <v>61</v>
@@ -11282,7 +11270,7 @@
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B283" s="5" t="s">
         <v>66</v>
@@ -11311,16 +11299,16 @@
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="8" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B284" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C284" s="9" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="D284" s="9" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E284" s="9" t="s">
         <v>47</v>
@@ -11340,16 +11328,16 @@
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B285" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E285" s="5" t="s">
         <v>47</v>
@@ -11369,16 +11357,16 @@
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B286" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C286" s="9" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D286" s="9" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E286" s="9" t="s">
         <v>47</v>
@@ -11398,16 +11386,16 @@
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="E287" s="5" t="s">
         <v>47</v>
@@ -11427,16 +11415,16 @@
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="8" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B288" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C288" s="9" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="D288" s="9" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E288" s="9" t="s">
         <v>47</v>
@@ -11456,16 +11444,16 @@
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E289" s="5" t="s">
         <v>47</v>
@@ -11485,16 +11473,16 @@
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="8" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B290" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C290" s="9" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D290" s="9" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E290" s="9" t="s">
         <v>47</v>
@@ -11514,16 +11502,16 @@
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="E291" s="5" t="s">
         <v>47</v>
@@ -11543,16 +11531,16 @@
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B292" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C292" s="9" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="D292" s="9" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="E292" s="9" t="s">
         <v>47</v>
@@ -11572,16 +11560,16 @@
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="E293" s="5" t="s">
         <v>47</v>
@@ -11601,28 +11589,28 @@
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="8" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B294" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C294" s="9" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="D294" s="9" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="E294" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F294" s="9" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="G294" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="H294" s="12" t="s">
-        <v>133</v>
+      <c r="H294" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I294" s="9" t="s">
         <v>75</v>
@@ -11630,16 +11618,16 @@
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E295" s="5" t="s">
         <v>47</v>
@@ -11659,16 +11647,16 @@
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="8" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B296" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C296" s="9" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D296" s="9" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="E296" s="9" t="s">
         <v>47</v>
@@ -11688,16 +11676,16 @@
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="E297" s="5" t="s">
         <v>47</v>
@@ -11717,16 +11705,16 @@
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B298" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C298" s="9" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D298" s="9" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="E298" s="9" t="s">
         <v>47</v>
@@ -11746,16 +11734,16 @@
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="E299" s="5" t="s">
         <v>47</v>
@@ -11775,16 +11763,16 @@
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="8" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B300" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C300" s="9" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="D300" s="9" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="E300" s="9" t="s">
         <v>47</v>
@@ -11804,16 +11792,16 @@
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="E301" s="5" t="s">
         <v>47</v>
@@ -11833,16 +11821,16 @@
     </row>
     <row r="302" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="8" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B302" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C302" s="9" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="D302" s="9" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="E302" s="9" t="s">
         <v>47</v>
@@ -11862,16 +11850,16 @@
     </row>
     <row r="303" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="E303" s="5" t="s">
         <v>47</v>
@@ -11891,16 +11879,16 @@
     </row>
     <row r="304" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B304" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C304" s="9" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="D304" s="9" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="E304" s="9" t="s">
         <v>125</v>
